--- a/Team-Data/2013-14/12-9-2013-14.xlsx
+++ b/Team-Data/2013-14/12-9-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -757,10 +824,10 @@
         <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
         <v>11</v>
@@ -772,10 +839,10 @@
         <v>13</v>
       </c>
       <c r="AO2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP2" t="n">
         <v>22</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>19</v>
@@ -793,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>13</v>
@@ -939,10 +1006,10 @@
         <v>19</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL3" t="n">
         <v>22</v>
@@ -963,16 +1030,16 @@
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV3" t="n">
         <v>24</v>
@@ -990,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
@@ -1112,10 +1179,10 @@
         <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
@@ -1142,22 +1209,22 @@
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1207,94 +1274,94 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.476</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
       <c r="J5" t="n">
-        <v>80.5</v>
+        <v>79.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.414</v>
+        <v>0.412</v>
       </c>
       <c r="L5" t="n">
         <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.295</v>
+        <v>0.287</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.707</v>
+        <v>0.702</v>
       </c>
       <c r="R5" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="S5" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="T5" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U5" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V5" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA5" t="n">
         <v>22.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>90.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>23</v>
@@ -1303,13 +1370,13 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM5" t="n">
         <v>29</v>
@@ -1327,19 +1394,19 @@
         <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
         <v>28</v>
@@ -1351,13 +1418,13 @@
         <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
@@ -1488,7 +1555,7 @@
         <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1500,13 +1567,13 @@
         <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1527,7 +1594,7 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1536,7 +1603,7 @@
         <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-7.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1667,7 +1734,7 @@
         <v>26</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1682,34 +1749,34 @@
         <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
       </c>
       <c r="AW7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX7" t="n">
         <v>16</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>17</v>
       </c>
       <c r="AY7" t="n">
         <v>24</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
         <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.591</v>
+        <v>0.619</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J8" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="M8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.379</v>
+        <v>0.39</v>
       </c>
       <c r="O8" t="n">
         <v>17</v>
@@ -1792,7 +1859,7 @@
         <v>20.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
@@ -1801,16 +1868,16 @@
         <v>30.8</v>
       </c>
       <c r="T8" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V8" t="n">
         <v>14.7</v>
       </c>
       <c r="W8" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="X8" t="n">
         <v>4.4</v>
@@ -1819,28 +1886,28 @@
         <v>3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.4</v>
+        <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>23</v>
@@ -1849,16 +1916,16 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK8" t="n">
         <v>7</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>8</v>
@@ -1876,37 +1943,37 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU8" t="n">
         <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -1935,100 +2002,100 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.619</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M9" t="n">
         <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>25.6</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.714</v>
+        <v>0.718</v>
       </c>
       <c r="R9" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S9" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
         <v>46.1</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="V9" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y9" t="n">
         <v>5.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.6</v>
+        <v>104</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
         <v>9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
         <v>6</v>
@@ -2046,7 +2113,7 @@
         <v>10</v>
       </c>
       <c r="AO9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2061,16 +2128,16 @@
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2079,13 +2146,13 @@
         <v>23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -2195,16 +2262,16 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -2213,7 +2280,7 @@
         <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
         <v>16</v>
@@ -2225,7 +2292,7 @@
         <v>21</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
@@ -2255,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2267,7 +2334,7 @@
         <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -2299,112 +2366,112 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.545</v>
+        <v>0.571</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J11" t="n">
-        <v>81.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K11" t="n">
         <v>0.469</v>
       </c>
       <c r="L11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.417</v>
+        <v>0.427</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
         <v>22.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="R11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="U11" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="X11" t="n">
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
         <v>22.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>103</v>
+        <v>102.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
         <v>4</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2422,22 +2489,22 @@
         <v>26</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
@@ -2446,10 +2513,10 @@
         <v>26</v>
       </c>
       <c r="BA11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>6.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
         <v>1</v>
@@ -2610,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2625,7 +2692,7 @@
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2759,10 +2826,10 @@
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
         <v>17</v>
@@ -2777,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2786,16 +2853,16 @@
         <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -2845,85 +2912,85 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.636</v>
+        <v>0.619</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
         <v>82.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L14" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="O14" t="n">
         <v>19.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.709</v>
+        <v>0.711</v>
       </c>
       <c r="R14" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X14" t="n">
         <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z14" t="n">
         <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.1</v>
+        <v>104.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2935,10 +3002,10 @@
         <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
         <v>16</v>
@@ -2953,7 +3020,7 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
@@ -2965,10 +3032,10 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2977,16 +3044,16 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ14" t="n">
         <v>27</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-2</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -3126,7 +3193,7 @@
         <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
         <v>1</v>
@@ -3147,7 +3214,7 @@
         <v>24</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS15" t="n">
         <v>8</v>
@@ -3162,7 +3229,7 @@
         <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX15" t="n">
         <v>5</v>
@@ -3171,7 +3238,7 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="H16" t="n">
         <v>48.5</v>
@@ -3227,115 +3294,115 @@
         <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="M16" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.772</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
         <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="T16" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
         <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.8</v>
+        <v>-3.4</v>
       </c>
       <c r="AD16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE16" t="n">
         <v>16</v>
       </c>
-      <c r="AE16" t="n">
-        <v>13</v>
-      </c>
       <c r="AF16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH16" t="n">
         <v>11</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>12</v>
       </c>
       <c r="AI16" t="n">
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM16" t="n">
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,16 +3411,16 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>20</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3502,7 +3569,7 @@
         <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
@@ -3529,19 +3596,19 @@
         <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA17" t="n">
         <v>12</v>
       </c>
-      <c r="BA17" t="n">
-        <v>11</v>
-      </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3669,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3693,7 +3760,7 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -3714,16 +3781,16 @@
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>2.8</v>
       </c>
       <c r="AD19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE19" t="n">
         <v>16</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
         <v>18</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
@@ -3863,7 +3930,7 @@
         <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3878,13 +3945,13 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>4</v>
@@ -4048,13 +4115,13 @@
         <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>2</v>
@@ -4063,7 +4130,7 @@
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>12</v>
@@ -4081,13 +4148,13 @@
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA20" t="n">
         <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>25</v>
@@ -4218,10 +4285,10 @@
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
@@ -4266,7 +4333,7 @@
         <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4391,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
@@ -4436,7 +4503,7 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>4</v>
@@ -4448,7 +4515,7 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4483,106 +4550,106 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.286</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M23" t="n">
         <v>21.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.754</v>
+        <v>0.745</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="V23" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="W23" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>15</v>
@@ -4594,46 +4661,46 @@
         <v>15</v>
       </c>
       <c r="AO23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP23" t="n">
         <v>21</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV23" t="n">
         <v>26</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AY23" t="n">
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
         <v>25</v>
       </c>
       <c r="BB23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BC23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4665,91 +4732,91 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="H24" t="n">
         <v>49.4</v>
       </c>
       <c r="I24" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="J24" t="n">
-        <v>89</v>
+        <v>88.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.448</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="M24" t="n">
         <v>22.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.312</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="R24" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S24" t="n">
         <v>34</v>
       </c>
       <c r="T24" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="U24" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="W24" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>102</v>
+        <v>102.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>22</v>
       </c>
       <c r="AF24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG24" t="n">
         <v>24</v>
@@ -4767,55 +4834,55 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT24" t="n">
         <v>5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>4</v>
-      </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>29</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
         <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC24" t="n">
         <v>27</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>17</v>
@@ -4946,7 +5013,7 @@
         <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -4961,7 +5028,7 @@
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ25" t="n">
         <v>21</v>
@@ -4970,7 +5037,7 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>19</v>
@@ -4991,7 +5058,7 @@
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5000,7 +5067,7 @@
         <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5029,88 +5096,88 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J26" t="n">
         <v>85.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.415</v>
+        <v>0.418</v>
       </c>
       <c r="O26" t="n">
         <v>18.2</v>
       </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S26" t="n">
         <v>32.5</v>
       </c>
       <c r="T26" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U26" t="n">
         <v>22.9</v>
       </c>
       <c r="V26" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W26" t="n">
         <v>6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z26" t="n">
         <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AB26" t="n">
         <v>106.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE26" t="n">
         <v>2</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
         <v>4</v>
@@ -5131,16 +5198,16 @@
         <v>10</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -5152,7 +5219,7 @@
         <v>5</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
         <v>7</v>
@@ -5161,13 +5228,13 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5182,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5211,94 +5278,94 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>0.316</v>
+        <v>0.278</v>
       </c>
       <c r="H27" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.432</v>
+        <v>0.43</v>
       </c>
       <c r="L27" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M27" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.336</v>
+        <v>0.334</v>
       </c>
       <c r="O27" t="n">
-        <v>18.4</v>
+        <v>17.9</v>
       </c>
       <c r="P27" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
         <v>11.4</v>
       </c>
       <c r="S27" t="n">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="T27" t="n">
-        <v>42.5</v>
+        <v>42.1</v>
       </c>
       <c r="U27" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V27" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
         <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
         <v>23.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.1</v>
+        <v>-3.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>10</v>
@@ -5307,46 +5374,46 @@
         <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS27" t="n">
         <v>21</v>
       </c>
-      <c r="AO27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>17</v>
-      </c>
       <c r="AT27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
         <v>16</v>
       </c>
       <c r="AV27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5358,10 +5425,10 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5510,16 +5577,16 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5528,10 +5595,10 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5677,13 +5744,13 @@
         <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -5710,13 +5777,13 @@
         <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>28</v>
@@ -5725,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.174</v>
+        <v>0.182</v>
       </c>
       <c r="H30" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
         <v>34.8</v>
@@ -5781,40 +5848,40 @@
         <v>0.429</v>
       </c>
       <c r="L30" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="M30" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.326</v>
+        <v>0.329</v>
       </c>
       <c r="O30" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P30" t="n">
         <v>22.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
       <c r="R30" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="V30" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="W30" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5823,13 +5890,13 @@
         <v>5</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AC30" t="n">
         <v>-10</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>17</v>
@@ -5874,19 +5941,19 @@
         <v>16</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
         <v>30</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
         <v>27</v>
@@ -5895,16 +5962,16 @@
         <v>19</v>
       </c>
       <c r="AX30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
@@ -5939,94 +6006,94 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>0.45</v>
+        <v>0.474</v>
       </c>
       <c r="H31" t="n">
         <v>49.3</v>
       </c>
       <c r="I31" t="n">
-        <v>36.9</v>
+        <v>37.1</v>
       </c>
       <c r="J31" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.44</v>
+        <v>0.445</v>
       </c>
       <c r="L31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M31" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.384</v>
+        <v>0.394</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.736</v>
+        <v>0.74</v>
       </c>
       <c r="R31" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="S31" t="n">
         <v>31.1</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W31" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
         <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE31" t="n">
         <v>16</v>
       </c>
-      <c r="AE31" t="n">
-        <v>18</v>
-      </c>
       <c r="AF31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>2</v>
@@ -6038,46 +6105,46 @@
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN31" t="n">
         <v>7</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AP31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT31" t="n">
         <v>22</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
@@ -6086,10 +6153,10 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-9-2013-14</t>
+          <t>2013-12-09</t>
         </is>
       </c>
     </row>
